--- a/real_estate_agent_forms/002_property_inquiry_form--real_estate_agent_forms.xlsx
+++ b/real_estate_agent_forms/002_property_inquiry_form--real_estate_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'name':_'property_type_1',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'name': 'property_type_1', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'name':_'property_type_2',_'label':_'multi-unit'}</t>
+          <t>multi-unit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'name': 'property_type_2', 'label': 'Multi-unit'}</t>
+          <t>Multi-unit</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'name':_'property_type_3',_'label':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'name': 'property_type_3', 'label': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'name':_'price_range_1',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'name': 'price_range_1', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'name':_'price_range_2',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'name': 'price_range_2', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'name':_'price_range_3',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'name': 'price_range_3', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
